--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0008_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0008_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1098,7 +1099,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B28" s="0">
         <v>0</v>
@@ -1183,10 +1184,10 @@
         <v>0.062136217806464646</v>
       </c>
       <c r="D30" s="0">
-        <v>0.024042507152645855</v>
+        <v>0.024042507152645856</v>
       </c>
       <c r="E30" s="0">
-        <v>0.12589874399594247</v>
+        <v>0.12589874399594248</v>
       </c>
       <c r="F30" s="0">
         <v>0.018193064803696816</v>
@@ -1417,7 +1418,7 @@
         <v>2.7870759867537789</v>
       </c>
       <c r="F36" s="0">
-        <v>1.7156060109886095</v>
+        <v>1.7156060109886096</v>
       </c>
       <c r="G36" s="0">
         <v>3.4198350432508522</v>
@@ -1455,7 +1456,7 @@
         <v>3.3258748769354667</v>
       </c>
       <c r="F37" s="0">
-        <v>2.4469672160972213</v>
+        <v>2.4469672160972214</v>
       </c>
       <c r="G37" s="0">
         <v>4.1038020519010221</v>
@@ -1671,7 +1672,7 @@
         <v>3.5148173673328706</v>
       </c>
       <c r="B43" s="0">
-        <v>4.5614035087719262</v>
+        <v>4.5614035087719263</v>
       </c>
       <c r="C43" s="0">
         <v>4.1288882689356914</v>
@@ -1698,7 +1699,7 @@
         <v>3.4596981965402991</v>
       </c>
       <c r="K43" s="0">
-        <v>4.3814432989690681</v>
+        <v>4.3814432989690682</v>
       </c>
       <c r="L43" s="0">
         <v>3.6435169346561724</v>
@@ -1896,7 +1897,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>2.86009648518263</v>
+        <v>2.8600964851826301</v>
       </c>
       <c r="B49" s="0">
         <v>0.87719298245613953</v>
@@ -1967,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="L50" s="0">
-        <v>2.5083195969271896</v>
+        <v>2.5083195969271897</v>
       </c>
     </row>
     <row r="51">
@@ -2227,13 +2228,13 @@
         <v>1.7238982343945679</v>
       </c>
       <c r="J57" s="0">
-        <v>1.472211998527803</v>
+        <v>1.4722119985278031</v>
       </c>
       <c r="K57" s="0">
         <v>0.25773195876288924</v>
       </c>
       <c r="L57" s="0">
-        <v>1.8100954809815752</v>
+        <v>1.8100954809815753</v>
       </c>
     </row>
     <row r="58">
@@ -2279,7 +2280,7 @@
         <v>1.9518558629516574</v>
       </c>
       <c r="B59" s="0">
-        <v>2.1052631578947349</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="C59" s="0">
         <v>1.7296694099595464</v>
@@ -2297,10 +2298,10 @@
         <v>2.1726010863005412</v>
       </c>
       <c r="H59" s="0">
-        <v>2.0962335965460412</v>
+        <v>2.0962335965460413</v>
       </c>
       <c r="I59" s="0">
-        <v>1.4518083056940267</v>
+        <v>1.4518083056940268</v>
       </c>
       <c r="J59" s="0">
         <v>1.9138755980861226</v>
@@ -2309,7 +2310,7 @@
         <v>0.90206185567010222</v>
       </c>
       <c r="L59" s="0">
-        <v>1.5643952352813097</v>
+        <v>1.5643952352813098</v>
       </c>
     </row>
     <row r="60">
@@ -2437,7 +2438,7 @@
         <v>1.3872861689851494</v>
       </c>
       <c r="D63" s="0">
-        <v>1.3271463948260513</v>
+        <v>1.3271463948260514</v>
       </c>
       <c r="E63" s="0">
         <v>1.6193800531042082</v>
@@ -2461,7 +2462,7 @@
         <v>0.90206185567010222</v>
       </c>
       <c r="L63" s="0">
-        <v>1.2720430441949417</v>
+        <v>1.2720430441949418</v>
       </c>
     </row>
     <row r="64">
@@ -2487,7 +2488,7 @@
         <v>1.4685174009253659</v>
       </c>
       <c r="H64" s="0">
-        <v>1.3974890643640276</v>
+        <v>1.3974890643640277</v>
       </c>
       <c r="I64" s="0">
         <v>1.0804154833071826</v>
@@ -2563,7 +2564,7 @@
         <v>1.2673506336753158</v>
       </c>
       <c r="H66" s="0">
-        <v>1.2043401692893247</v>
+        <v>1.2043401692893248</v>
       </c>
       <c r="I66" s="0">
         <v>0.92947508490397324</v>
@@ -2656,7 +2657,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.090381018017142</v>
+        <v>1.0903810180171421</v>
       </c>
       <c r="B69" s="0">
         <v>0.087719298245614932</v>
@@ -2756,7 +2757,7 @@
         <v>0.99414872464920667</v>
       </c>
       <c r="I71" s="0">
-        <v>0.62163611447637523</v>
+        <v>0.62163611447637524</v>
       </c>
       <c r="J71" s="0">
         <v>1.0121457489878534</v>
@@ -2829,7 +2830,7 @@
         <v>0.84490042245021046</v>
       </c>
       <c r="H73" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.67602113276146048</v>
       </c>
       <c r="I73" s="0">
         <v>0.55808226251712922</v>
@@ -2864,7 +2865,7 @@
         <v>0.83142306152894441</v>
       </c>
       <c r="G74" s="0">
-        <v>0.6638503319251654</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H74" s="0">
         <v>0.73851048116798212</v>
@@ -2879,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.67023294871396077</v>
+        <v>0.67023294871396078</v>
       </c>
     </row>
     <row r="75">
@@ -2908,7 +2909,7 @@
         <v>0.73282963131284373</v>
       </c>
       <c r="I75" s="0">
-        <v>0.44289090584099577</v>
+        <v>0.44289090584099578</v>
       </c>
       <c r="J75" s="0">
         <v>0.60728744939271206</v>
@@ -2917,7 +2918,7 @@
         <v>0.12886597938144317</v>
       </c>
       <c r="L75" s="0">
-        <v>0.70133424563804247</v>
+        <v>0.70133424563804248</v>
       </c>
     </row>
     <row r="76">
@@ -2946,7 +2947,7 @@
         <v>0.73282963131284373</v>
       </c>
       <c r="I76" s="0">
-        <v>0.44289090584099577</v>
+        <v>0.44289090584099578</v>
       </c>
       <c r="J76" s="0">
         <v>0.73610599926389342</v>
@@ -2960,7 +2961,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.58580289455547851</v>
+        <v>0.58580289455547852</v>
       </c>
       <c r="B77" s="0">
         <v>1.3157894736842093</v>
@@ -3010,7 +3011,7 @@
         <v>0.27408458154016274</v>
       </c>
       <c r="E78" s="0">
-        <v>0.40335332199647927</v>
+        <v>0.40335332199647928</v>
       </c>
       <c r="F78" s="0">
         <v>0.73318051158898168</v>
@@ -3019,7 +3020,7 @@
         <v>0.60350030175015035</v>
       </c>
       <c r="H78" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.67602113276146048</v>
       </c>
       <c r="I78" s="0">
         <v>0.35550435939703251</v>
@@ -3036,13 +3037,13 @@
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.5759574677562268</v>
+        <v>0.57595746775622681</v>
       </c>
       <c r="B79" s="0">
         <v>0.78947368421052566</v>
       </c>
       <c r="C79" s="0">
-        <v>0.40578754485854462</v>
+        <v>0.40578754485854463</v>
       </c>
       <c r="D79" s="0">
         <v>0.25244632510278148</v>
@@ -3145,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>0.42142257332130711</v>
+        <v>0.42142257332130712</v>
       </c>
     </row>
     <row r="82">
@@ -3168,16 +3169,16 @@
         <v>0.49121274969981948</v>
       </c>
       <c r="G82" s="0">
-        <v>0.341983504325089</v>
+        <v>0.34198350432508901</v>
       </c>
       <c r="H82" s="0">
         <v>0.38061694029427195</v>
       </c>
       <c r="I82" s="0">
-        <v>0.24031300272090172</v>
+        <v>0.24031300272090173</v>
       </c>
       <c r="J82" s="0">
-        <v>0.55207949944792611</v>
+        <v>0.55207949944792612</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
@@ -3232,7 +3233,7 @@
         <v>0.35087719298245584</v>
       </c>
       <c r="C84" s="0">
-        <v>0.14963415716658834</v>
+        <v>0.14963415716658835</v>
       </c>
       <c r="D84" s="0">
         <v>0.12021253576322928</v>
@@ -3273,7 +3274,7 @@
         <v>0.11666391914683158</v>
       </c>
       <c r="D85" s="0">
-        <v>0.12261678647849387</v>
+        <v>0.12261678647849388</v>
       </c>
       <c r="E85" s="0">
         <v>0.17542289447775875</v>
@@ -3460,7 +3461,7 @@
         <v>0.087719298245613961</v>
       </c>
       <c r="C90" s="0">
-        <v>0.040578754485854462</v>
+        <v>0.040578754485854463</v>
       </c>
       <c r="D90" s="0">
         <v>0.086553025749525073</v>
@@ -3796,7 +3797,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B99" s="0">
         <v>0.087719298245613961</v>
@@ -3834,7 +3835,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B100" s="0">
         <v>1.0526315789473675</v>
